--- a/Assets/Data/Dungeon0063.xlsx
+++ b/Assets/Data/Dungeon0063.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="14">
   <si>
     <t>Id</t>
   </si>
@@ -42,7 +42,16 @@
     <t>InitDir</t>
   </si>
   <si>
+    <t>□</t>
+  </si>
+  <si>
     <t>■</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>◆</t>
   </si>
   <si>
     <t>Mv</t>
@@ -58,8 +67,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -78,14 +87,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -106,93 +147,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,11 +183,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -230,7 +239,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -242,13 +275,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -260,31 +347,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,19 +365,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -326,37 +395,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,49 +413,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,50 +433,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -483,6 +453,32 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -511,12 +507,25 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -529,145 +538,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1261,37 +1270,37 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>8</v>
@@ -1332,19 +1341,37 @@
         <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="M4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>8</v>
@@ -1385,33 +1412,37 @@
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L5" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="M5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>8</v>
@@ -1452,25 +1483,37 @@
         <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J6" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L6" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="M6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>8</v>
@@ -1511,31 +1554,37 @@
         <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L7" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="M7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>8</v>
@@ -1576,33 +1625,37 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>8</v>
@@ -1643,33 +1696,37 @@
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>8</v>
@@ -1710,26 +1767,28 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>8</v>
@@ -1775,14 +1834,16 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E11" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>8</v>
@@ -1840,16 +1901,16 @@
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>8</v>
@@ -3245,43 +3306,43 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -3316,43 +3377,43 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -3387,10 +3448,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -3402,10 +3463,10 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
@@ -3440,39 +3501,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -3507,31 +3568,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -3566,37 +3627,37 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -3631,39 +3692,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -3698,39 +3759,39 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -3765,41 +3826,41 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -3830,41 +3891,41 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -3895,43 +3956,43 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -3965,43 +4026,43 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -4033,43 +4094,43 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>

--- a/Assets/Data/Dungeon0063.xlsx
+++ b/Assets/Data/Dungeon0063.xlsx
@@ -96,10 +96,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -124,23 +124,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,32 +139,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -194,7 +155,53 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -209,24 +216,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -239,10 +239,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -255,7 +255,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,7 +270,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,73 +306,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -366,7 +330,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -378,31 +408,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,19 +426,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,18 +451,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,23 +467,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -518,20 +503,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -547,6 +529,24 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,145 +569,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -823,169 +823,177 @@
         </row>
         <row r="4">
           <cell r="D4">
-            <v>2010</v>
+            <v>1020</v>
           </cell>
           <cell r="E4" t="str">
-            <v>ダンジョンから出る</v>
+            <v>エンフェリアイベント再生</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2021</v>
+            <v>2020</v>
           </cell>
           <cell r="E6" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2030</v>
+            <v>2021</v>
           </cell>
           <cell r="E7" t="str">
-            <v>ダンジョンクリア</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>3010</v>
+            <v>2030</v>
           </cell>
           <cell r="E8" t="str">
-            <v>アーティファクト取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3020</v>
+            <v>3010</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アイテム取得</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3030</v>
+            <v>3020</v>
           </cell>
           <cell r="E10" t="str">
-            <v>魔法入手</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>4010</v>
+            <v>3030</v>
           </cell>
           <cell r="E11" t="str">
-            <v>仲間を増やす</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4011</v>
+            <v>4010</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を外す</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4020</v>
+            <v>4011</v>
           </cell>
           <cell r="E13" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>5010</v>
+            <v>4020</v>
           </cell>
           <cell r="E14" t="str">
-            <v>強制戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5020</v>
+            <v>5010</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制ボス戦闘</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>6010</v>
+            <v>5020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6011</v>
+            <v>6010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6020</v>
+            <v>6011</v>
           </cell>
           <cell r="E18" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6030</v>
+            <v>6020</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>7010</v>
+            <v>6030</v>
           </cell>
           <cell r="E20" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7020</v>
+            <v>7010</v>
           </cell>
           <cell r="E21" t="str">
-            <v>怨嗟床</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7021</v>
+            <v>7020</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床解除</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>8010</v>
+            <v>7021</v>
           </cell>
           <cell r="E23" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床解除</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
+            <v>8010</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
             <v>9010</v>
           </cell>
-          <cell r="E24" t="str">
+          <cell r="E25" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -5514,8 +5522,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
+  <cols>
+    <col min="7" max="7" width="16.7272727272727" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -5813,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -5896,23 +5907,56 @@
         <v>3010</v>
       </c>
       <c r="F12">
-        <v>9010</v>
+        <v>1020</v>
       </c>
       <c r="G12" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F12,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>エンフェリアイベント再生</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>63</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>3010</v>
+      </c>
+      <c r="F13">
+        <v>9010</v>
+      </c>
+      <c r="G13" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
+        <v>イベント終了明示</v>
+      </c>
+      <c r="H13">
         <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
